--- a/astro-site/public/dl/guia-restaurante-gastronomico/checklist-contratacion.xlsx
+++ b/astro-site/public/dl/guia-restaurante-gastronomico/checklist-contratacion.xlsx
@@ -11,6 +11,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet'!$A$4:$H$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Sheet'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -489,7 +490,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -518,6 +519,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1460,6 +1462,7 @@
       </c>
       <c r="H34" s="6" t="n"/>
     </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
@@ -1479,6 +1482,15 @@
       <formula1>"Pendiente,En Curso,Completado"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/guia-restaurante-gastronomico/checklist-contratacion.xlsx
+++ b/astro-site/public/dl/guia-restaurante-gastronomico/checklist-contratacion.xlsx
@@ -7,11 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contratación Equipo" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet'!$A$4:$H$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Sheet'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Contratación Equipo'!$A$4:$H$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Contratación Equipo'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,10 +20,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.00 €"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,8 +61,25 @@
       <color rgb="00888888"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font/>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -76,6 +96,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="00E8F5E9"/>
         <bgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -105,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -127,10 +152,73 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
+          <bgColor rgb="00C6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="009C6500"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFEB9C"/>
+          <bgColor rgb="00FFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00595959"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00F2F2F2"/>
+          <bgColor rgb="00F2F2F2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -492,16 +580,113 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="80" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Checklist Contratación Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AI Chef Pro · aichef.pro — Restaurante Gastronómico</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Instrucciones de uso</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1. Rellena las celdas verdes con tus datos; el resto lo calcula el libro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2. Las hojas están protegidas SIN contraseña para que una copia accidental no borre una fórmula.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Celdas verdes = campos editables</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>Para editar la estructura o una celda que no esté en verde: Revisar → Desproteger hoja (no tiene contraseña).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/guia-restaurante-gastronomico · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -576,21 +761,21 @@
           <t>Definir organigrama completo (cocina + sala)</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>Chef + Maître</t>
         </is>
       </c>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="6" t="n"/>
+      <c r="E5" s="13" t="n"/>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -606,21 +791,21 @@
           <t>Fichas de puesto: funciones, requisitos, salario</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>RRHH</t>
         </is>
       </c>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="6" t="n"/>
+      <c r="E6" s="13" t="n"/>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="12" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -636,21 +821,21 @@
           <t>Chef Ejecutivo: experiencia mínima 5 años en fine dining</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>Propietario</t>
         </is>
       </c>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="6" t="n"/>
+      <c r="E7" s="13" t="n"/>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="12" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -666,21 +851,21 @@
           <t>Sous Chef: experiencia mínima 3 años en gastronómico</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>Chef</t>
         </is>
       </c>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="6" t="n"/>
+      <c r="E8" s="13" t="n"/>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -696,21 +881,21 @@
           <t>Sommelier: certificación WSET o equivalente</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>Maître</t>
         </is>
       </c>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="6" t="n"/>
+      <c r="E9" s="13" t="n"/>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="12" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -726,21 +911,21 @@
           <t>Maître: experiencia mínima 3 años en sala premium</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>Propietario</t>
         </is>
       </c>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="6" t="n"/>
+      <c r="E10" s="13" t="n"/>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -756,21 +941,21 @@
           <t>Publicar ofertas en portales especializados (Hostelería)</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>RRHH</t>
         </is>
       </c>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="n">
+      <c r="E11" s="13" t="n"/>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G11" s="14" t="n">
         <v>200</v>
       </c>
-      <c r="H11" s="6" t="n"/>
+      <c r="H11" s="12" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -786,21 +971,21 @@
           <t>Contactar escuelas de hostelería (BCC, Hofmann, etc.)</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t>Chef</t>
         </is>
       </c>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="6" t="n"/>
+      <c r="E12" s="13" t="n"/>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="12" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -816,21 +1001,21 @@
           <t>Pruebas prácticas para cocineros (cocinar un plato)</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t>Chef</t>
         </is>
       </c>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="6" t="n"/>
+      <c r="E13" s="13" t="n"/>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="12" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -846,21 +1031,21 @@
           <t>Entrevistas de servicio para personal de sala</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>Maître</t>
         </is>
       </c>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="6" t="n"/>
+      <c r="E14" s="13" t="n"/>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="12" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -876,21 +1061,21 @@
           <t>Verificar referencias de empleos anteriores</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t>RRHH</t>
         </is>
       </c>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="6" t="n"/>
+      <c r="E15" s="13" t="n"/>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -903,24 +1088,24 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Stage de prueba (1-3 días) antes de contrato definitivo</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
+          <t>Stage de prueba (1‑3 días) antes de contrato definitivo</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>Chef/Maître</t>
         </is>
       </c>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="6" t="n"/>
+      <c r="E16" s="13" t="n"/>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="12" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -936,21 +1121,21 @@
           <t>Contrato de trabajo (modalidad según puesto)</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="12" t="inlineStr">
         <is>
           <t>Asesor laboral</t>
         </is>
       </c>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G17" s="7" t="n">
+      <c r="E17" s="13" t="n"/>
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G17" s="14" t="n">
         <v>300</v>
       </c>
-      <c r="H17" s="6" t="n"/>
+      <c r="H17" s="12" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -966,21 +1151,21 @@
           <t>Alta en Seguridad Social</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>Asesor laboral</t>
         </is>
       </c>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="6" t="n"/>
+      <c r="E18" s="13" t="n"/>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="12" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -996,21 +1181,21 @@
           <t>Certificado manipulador alimentos</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="12" t="inlineStr">
         <is>
           <t>Empleado</t>
         </is>
       </c>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G19" s="7" t="n">
+      <c r="E19" s="13" t="n"/>
+      <c r="F19" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G19" s="14" t="n">
         <v>50</v>
       </c>
-      <c r="H19" s="6" t="n"/>
+      <c r="H19" s="12" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -1023,24 +1208,28 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Cláusula de confidencialidad y no competencia (chef)</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
+          <t>Pacto de no competencia postcontractual CON compensación económica pactada (art. 21.2 ET; máx. 2 años para técnicos)</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
         <is>
           <t>Abogado</t>
         </is>
       </c>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G20" s="7" t="n">
+      <c r="E20" s="13" t="n"/>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G20" s="14" t="n">
         <v>200</v>
       </c>
-      <c r="H20" s="6" t="n"/>
+      <c r="H20" s="12" t="inlineStr">
+        <is>
+          <t>Sin compensación económica adecuada el pacto es NULO. La confidencialidad durante el contrato es otra cosa y sí se puede pactar sin compensación. Registro retributivo y protocolo de acoso están en el checklist legal, categoría Laboral.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -1056,21 +1245,21 @@
           <t>Reconocimiento médico inicial</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="12" t="inlineStr">
         <is>
           <t>Mutua</t>
         </is>
       </c>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G21" s="7" t="n">
+      <c r="E21" s="13" t="n"/>
+      <c r="F21" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G21" s="14" t="n">
         <v>60</v>
       </c>
-      <c r="H21" s="6" t="n"/>
+      <c r="H21" s="12" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -1086,21 +1275,21 @@
           <t>Manual de bienvenida y procedimientos</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" s="12" t="inlineStr">
         <is>
           <t>Chef/Maître</t>
         </is>
       </c>
-      <c r="E22" s="6" t="n"/>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="6" t="n"/>
+      <c r="E22" s="13" t="n"/>
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G22" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="12" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -1116,21 +1305,21 @@
           <t>Formación APPCC y alérgenos (primer día)</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D23" s="12" t="inlineStr">
         <is>
           <t>Resp. APPCC</t>
         </is>
       </c>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="6" t="n"/>
+      <c r="E23" s="13" t="n"/>
+      <c r="F23" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G23" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="12" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -1146,21 +1335,21 @@
           <t>Tour completo de instalaciones</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D24" s="12" t="inlineStr">
         <is>
           <t>Sous Chef</t>
         </is>
       </c>
-      <c r="E24" s="6" t="n"/>
-      <c r="F24" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="6" t="n"/>
+      <c r="E24" s="13" t="n"/>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G24" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="12" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -1176,21 +1365,21 @@
           <t>Asignación de uniforme y taquilla</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D25" s="12" t="inlineStr">
         <is>
           <t>RRHH</t>
         </is>
       </c>
-      <c r="E25" s="6" t="n"/>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G25" s="7" t="n">
+      <c r="E25" s="13" t="n"/>
+      <c r="F25" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G25" s="14" t="n">
         <v>200</v>
       </c>
-      <c r="H25" s="6" t="n"/>
+      <c r="H25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -1206,21 +1395,21 @@
           <t>Presentación al equipo completo</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D26" s="12" t="inlineStr">
         <is>
           <t>Chef/Maître</t>
         </is>
       </c>
-      <c r="E26" s="6" t="n"/>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G26" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="6" t="n"/>
+      <c r="E26" s="13" t="n"/>
+      <c r="F26" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G26" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="12" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -1233,24 +1422,24 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Sesiones de entrenamiento pre-apertura (2-4 semanas)</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
+          <t>Sesiones de entrenamiento pre-apertura (2‑4 semanas)</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
         <is>
           <t>Chef</t>
         </is>
       </c>
-      <c r="E27" s="6" t="n"/>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G27" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="6" t="n"/>
+      <c r="E27" s="13" t="n"/>
+      <c r="F27" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G27" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="12" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -1266,21 +1455,21 @@
           <t>Formación en carta de vinos y maridajes (sala)</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D28" s="12" t="inlineStr">
         <is>
           <t>Sommelier</t>
         </is>
       </c>
-      <c r="E28" s="6" t="n"/>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G28" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="6" t="n"/>
+      <c r="E28" s="13" t="n"/>
+      <c r="F28" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G28" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="12" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
@@ -1296,21 +1485,21 @@
           <t>Protocolo de servicio de sala (manual)</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D29" s="12" t="inlineStr">
         <is>
           <t>Maître</t>
         </is>
       </c>
-      <c r="E29" s="6" t="n"/>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G29" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="6" t="n"/>
+      <c r="E29" s="13" t="n"/>
+      <c r="F29" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G29" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="12" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
@@ -1326,21 +1515,21 @@
           <t>Simulacro de servicio completo (soft opening)</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D30" s="12" t="inlineStr">
         <is>
           <t>Todo equipo</t>
         </is>
       </c>
-      <c r="E30" s="6" t="n"/>
-      <c r="F30" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G30" s="7" t="n">
+      <c r="E30" s="13" t="n"/>
+      <c r="F30" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G30" s="14" t="n">
         <v>500</v>
       </c>
-      <c r="H30" s="6" t="n"/>
+      <c r="H30" s="12" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -1356,21 +1545,21 @@
           <t>Convenio colectivo de hostelería aplicable</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D31" s="12" t="inlineStr">
         <is>
           <t>Asesor laboral</t>
         </is>
       </c>
-      <c r="E31" s="6" t="n"/>
-      <c r="F31" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G31" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="6" t="n"/>
+      <c r="E31" s="13" t="n"/>
+      <c r="F31" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G31" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="12" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
@@ -1386,21 +1575,21 @@
           <t>Cuadro horario visible en el centro de trabajo</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D32" s="12" t="inlineStr">
         <is>
           <t>RRHH</t>
         </is>
       </c>
-      <c r="E32" s="6" t="n"/>
-      <c r="F32" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="6" t="n"/>
+      <c r="E32" s="13" t="n"/>
+      <c r="F32" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G32" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="12" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
@@ -1416,21 +1605,25 @@
           <t>Registro de jornada digital (obligatorio)</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D33" s="12" t="inlineStr">
         <is>
           <t>RRHH</t>
         </is>
       </c>
-      <c r="E33" s="6" t="n"/>
-      <c r="F33" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G33" s="7" t="n">
+      <c r="E33" s="13" t="n"/>
+      <c r="F33" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G33" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="H33" s="6" t="n"/>
+      <c r="H33" s="12" t="inlineStr">
+        <is>
+          <t>Es la implantación del sistema de fichaje. La obligación y la conservación 4 años están en el checklist legal, categoría Laboral: son la misma cosa, no dos gastos.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
@@ -1443,43 +1636,206 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Plan de igualdad (si &gt;50 empleados)</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
+          <t>Plan de igualdad (50 o más personas trabajadoras)</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
         <is>
           <t>RRHH</t>
         </is>
       </c>
-      <c r="E34" s="6" t="n"/>
-      <c r="F34" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="G34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="6" t="n"/>
-    </row>
-    <row r="35"/>
+      <c r="E34" s="13" t="n"/>
+      <c r="F34" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="G34" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="12" t="inlineStr">
+        <is>
+          <t>El umbral es «50 o más», no «más de 50»: escrito con «&gt;50» dejaba fuera justo a la empresa de 50.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="E35" s="15" t="n"/>
+      <c r="G35" s="16" t="n"/>
+    </row>
     <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="A36" s="17" t="inlineStr">
+        <is>
+          <t>RESUMEN — lo calcula el libro (v2.0)</t>
+        </is>
+      </c>
+      <c r="B36" s="18" t="n"/>
+      <c r="C36" s="18" t="n"/>
+      <c r="D36" s="18" t="n"/>
+      <c r="E36" s="18" t="n"/>
+      <c r="F36" s="18" t="n"/>
+      <c r="G36" s="18" t="n"/>
+      <c r="H36" s="18" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>TOTAL PRESUPUESTADO (€)</t>
+        </is>
+      </c>
+      <c r="G37" s="20">
+        <f>SUM(G5:G34)</f>
+        <v>1610.0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>Partidas SIN importe (a presupuestar)</t>
+        </is>
+      </c>
+      <c r="G38" s="21">
+        <f>COUNTIF(B5:B34,"&lt;&gt;")-COUNT(G5:G34)</f>
+        <v>0.0</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>El TOTAL de arriba es un SUELO: no incluye estas partidas, que van a presupuestar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>Avance del checklist (% completado)</t>
+        </is>
+      </c>
+      <c r="F39" s="22">
+        <f>IFERROR(COUNTIF(F5:F34,"Completado")/COUNTIF(F5:F34,"&lt;&gt;"),"")</f>
+        <v>0.0</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Estado terminal de este checklist: «Completado»</t>
+        </is>
+      </c>
+    </row>
+    <row r="40"/>
+    <row r="41">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>SUBTOTALES POR CATEGORÍA</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Perfiles</t>
+        </is>
+      </c>
+      <c r="G42" s="16">
+        <f>SUMIF($B$5:$B$34,$A42,$G$5:$G$34)</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Selección</t>
+        </is>
+      </c>
+      <c r="G43" s="16">
+        <f>SUMIF($B$5:$B$34,$A43,$G$5:$G$34)</f>
+        <v>200.0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Documentación</t>
+        </is>
+      </c>
+      <c r="G44" s="16">
+        <f>SUMIF($B$5:$B$34,$A44,$G$5:$G$34)</f>
+        <v>610.0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="G45" s="16">
+        <f>SUMIF($B$5:$B$34,$A45,$G$5:$G$34)</f>
+        <v>200.0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Formación</t>
+        </is>
+      </c>
+      <c r="G46" s="16">
+        <f>SUMIF($B$5:$B$34,$A46,$G$5:$G$34)</f>
+        <v>500.0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="G47" s="16">
+        <f>SUMIF($B$5:$B$34,$A47,$G$5:$G$34)</f>
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="48"/>
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>AI Chef Pro · aichef.pro — Restaurante Gastronómico</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <autoFilter ref="A4:H4"/>
   <mergeCells count="3">
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A49:H49"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <conditionalFormatting sqref="F5:F34">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0" stopIfTrue="1">
+      <formula>"Completado"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1" stopIfTrue="1">
+      <formula>"En Curso"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2" stopIfTrue="1">
+      <formula>"Pendiente"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G38">
+    <cfRule type="expression" priority="4" dxfId="1" stopIfTrue="1">
+      <formula>=AND(ISNUMBER(G38),G38&gt;0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="3">
+    <dataValidation sqref="E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E32 E33 E34" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fecha no válida" error="Escribe una fecha (dd/mm/aaaa) entre 2020 y 2040." type="date" operator="between">
+      <formula1>DATE(2020,1,1)</formula1>
+      <formula2>DATE(2040,12,31)</formula2>
+    </dataValidation>
+    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor no válido" error="Elige un valor de la lista: Pendiente, En Curso, Completado" type="list">
       <formula1>"Pendiente,En Curso,Completado"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Importe no válido" error="Escribe un número mayor o igual que 0." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>

--- a/astro-site/public/dl/guia-restaurante-gastronomico/checklist-contratacion.xlsx
+++ b/astro-site/public/dl/guia-restaurante-gastronomico/checklist-contratacion.xlsx
@@ -130,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -177,6 +177,10 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1678,125 +1682,202 @@
       <c r="H36" s="18" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="19" t="inlineStr">
+      <c r="A37" s="17" t="inlineStr">
         <is>
           <t>TOTAL PRESUPUESTADO (€)</t>
         </is>
       </c>
-      <c r="G37" s="20">
+      <c r="B37" s="18" t="n"/>
+      <c r="C37" s="18" t="n"/>
+      <c r="D37" s="18" t="n"/>
+      <c r="E37" s="18" t="n"/>
+      <c r="F37" s="18" t="n"/>
+      <c r="G37" s="23">
         <f>SUM(G5:G34)</f>
         <v>1610.0</v>
       </c>
+      <c r="H37" s="18" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="19" t="inlineStr">
+      <c r="A38" s="17" t="inlineStr">
         <is>
           <t>Partidas SIN importe (a presupuestar)</t>
         </is>
       </c>
-      <c r="G38" s="21">
+      <c r="B38" s="18" t="n"/>
+      <c r="C38" s="18" t="n"/>
+      <c r="D38" s="18" t="n"/>
+      <c r="E38" s="18" t="n"/>
+      <c r="F38" s="18" t="n"/>
+      <c r="G38" s="24">
         <f>COUNTIF(B5:B34,"&lt;&gt;")-COUNT(G5:G34)</f>
         <v>0.0</v>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H38" s="18" t="inlineStr">
         <is>
           <t>El TOTAL de arriba es un SUELO: no incluye estas partidas, que van a presupuestar.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="19" t="inlineStr">
+      <c r="A39" s="17" t="inlineStr">
         <is>
           <t>Avance del checklist (% completado)</t>
         </is>
       </c>
-      <c r="F39" s="22">
+      <c r="B39" s="18" t="n"/>
+      <c r="C39" s="18" t="n"/>
+      <c r="D39" s="18" t="n"/>
+      <c r="E39" s="18" t="n"/>
+      <c r="F39" s="25">
         <f>IFERROR(COUNTIF(F5:F34,"Completado")/COUNTIF(F5:F34,"&lt;&gt;"),"")</f>
         <v>0.0</v>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G39" s="18" t="inlineStr">
         <is>
           <t>Estado terminal de este checklist: «Completado»</t>
         </is>
       </c>
-    </row>
-    <row r="40"/>
+      <c r="H39" s="18" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="18" t="n"/>
+      <c r="B40" s="18" t="n"/>
+      <c r="C40" s="18" t="n"/>
+      <c r="D40" s="18" t="n"/>
+      <c r="E40" s="18" t="n"/>
+      <c r="F40" s="18" t="n"/>
+      <c r="G40" s="18" t="n"/>
+      <c r="H40" s="18" t="n"/>
+    </row>
     <row r="41">
-      <c r="A41" s="19" t="inlineStr">
+      <c r="A41" s="17" t="inlineStr">
         <is>
           <t>SUBTOTALES POR CATEGORÍA</t>
         </is>
       </c>
+      <c r="B41" s="18" t="n"/>
+      <c r="C41" s="18" t="n"/>
+      <c r="D41" s="18" t="n"/>
+      <c r="E41" s="18" t="n"/>
+      <c r="F41" s="18" t="n"/>
+      <c r="G41" s="18" t="n"/>
+      <c r="H41" s="18" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="18" t="inlineStr">
         <is>
           <t>Perfiles</t>
         </is>
       </c>
-      <c r="G42" s="16">
+      <c r="B42" s="18" t="n"/>
+      <c r="C42" s="18" t="n"/>
+      <c r="D42" s="18" t="n"/>
+      <c r="E42" s="18" t="n"/>
+      <c r="F42" s="18" t="n"/>
+      <c r="G42" s="26">
         <f>SUMIF($B$5:$B$34,$A42,$G$5:$G$34)</f>
         <v>0.0</v>
       </c>
+      <c r="H42" s="18" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="18" t="inlineStr">
         <is>
           <t>Selección</t>
         </is>
       </c>
-      <c r="G43" s="16">
+      <c r="B43" s="18" t="n"/>
+      <c r="C43" s="18" t="n"/>
+      <c r="D43" s="18" t="n"/>
+      <c r="E43" s="18" t="n"/>
+      <c r="F43" s="18" t="n"/>
+      <c r="G43" s="26">
         <f>SUMIF($B$5:$B$34,$A43,$G$5:$G$34)</f>
         <v>200.0</v>
       </c>
+      <c r="H43" s="18" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="18" t="inlineStr">
         <is>
           <t>Documentación</t>
         </is>
       </c>
-      <c r="G44" s="16">
+      <c r="B44" s="18" t="n"/>
+      <c r="C44" s="18" t="n"/>
+      <c r="D44" s="18" t="n"/>
+      <c r="E44" s="18" t="n"/>
+      <c r="F44" s="18" t="n"/>
+      <c r="G44" s="26">
         <f>SUMIF($B$5:$B$34,$A44,$G$5:$G$34)</f>
         <v>610.0</v>
       </c>
+      <c r="H44" s="18" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="18" t="inlineStr">
         <is>
           <t>Onboarding</t>
         </is>
       </c>
-      <c r="G45" s="16">
+      <c r="B45" s="18" t="n"/>
+      <c r="C45" s="18" t="n"/>
+      <c r="D45" s="18" t="n"/>
+      <c r="E45" s="18" t="n"/>
+      <c r="F45" s="18" t="n"/>
+      <c r="G45" s="26">
         <f>SUMIF($B$5:$B$34,$A45,$G$5:$G$34)</f>
         <v>200.0</v>
       </c>
+      <c r="H45" s="18" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="18" t="inlineStr">
         <is>
           <t>Formación</t>
         </is>
       </c>
-      <c r="G46" s="16">
+      <c r="B46" s="18" t="n"/>
+      <c r="C46" s="18" t="n"/>
+      <c r="D46" s="18" t="n"/>
+      <c r="E46" s="18" t="n"/>
+      <c r="F46" s="18" t="n"/>
+      <c r="G46" s="26">
         <f>SUMIF($B$5:$B$34,$A46,$G$5:$G$34)</f>
         <v>500.0</v>
       </c>
+      <c r="H46" s="18" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="18" t="inlineStr">
         <is>
           <t>Legal</t>
         </is>
       </c>
-      <c r="G47" s="16">
+      <c r="B47" s="18" t="n"/>
+      <c r="C47" s="18" t="n"/>
+      <c r="D47" s="18" t="n"/>
+      <c r="E47" s="18" t="n"/>
+      <c r="F47" s="18" t="n"/>
+      <c r="G47" s="26">
         <f>SUMIF($B$5:$B$34,$A47,$G$5:$G$34)</f>
         <v>100.0</v>
       </c>
-    </row>
-    <row r="48"/>
+      <c r="H47" s="18" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="18" t="n"/>
+      <c r="B48" s="18" t="n"/>
+      <c r="C48" s="18" t="n"/>
+      <c r="D48" s="18" t="n"/>
+      <c r="E48" s="18" t="n"/>
+      <c r="F48" s="18" t="n"/>
+      <c r="G48" s="18" t="n"/>
+      <c r="H48" s="18" t="n"/>
+    </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="18" t="inlineStr">
         <is>
           <t>AI Chef Pro · aichef.pro — Restaurante Gastronómico</t>
         </is>
@@ -1811,13 +1892,13 @@
     <mergeCell ref="A49:H49"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:F34">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0" stopIfTrue="1">
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="0" stopIfTrue="1">
       <formula>"Completado"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1" stopIfTrue="1">
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="1" stopIfTrue="1">
       <formula>"En Curso"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2" stopIfTrue="1">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="2" stopIfTrue="1">
       <formula>"Pendiente"</formula>
     </cfRule>
   </conditionalFormatting>
